--- a/week-01/Ex4C_GTrends_marketing.xlsx
+++ b/week-01/Ex4C_GTrends_marketing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\disco\Documents\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F575AF0C-C6CD-4C8C-9ABE-9DABD1F76001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56C3A0C-E99D-4C43-8F1D-F1A264F5A863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="1" activeTab="2" xr2:uid="{8EC3B940-9E01-4E04-B968-15148883C8F1}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="25820" windowHeight="13900" firstSheet="1" activeTab="2" xr2:uid="{8EC3B940-9E01-4E04-B968-15148883C8F1}"/>
   </bookViews>
   <sheets>
     <sheet name="By Search Term" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -754,10 +754,10 @@
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="42" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2080,7 +2080,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{94374F2B-8AA9-4892-B41F-CBAE1C37A29D}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{94374F2B-8AA9-4892-B41F-CBAE1C37A29D}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A15:C26" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0">
@@ -2098,7 +2098,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisPage" showAll="0">
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
       <items count="3">
         <item x="1"/>
         <item x="0"/>
@@ -4125,7 +4125,7 @@
       <c r="B2" t="s">
         <v>61</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="4">
         <f>VLOOKUP('Sales Region Lookup'!A2, 'By Search Term'!B:C, 2, FALSE)</f>
         <v>0.67</v>
       </c>
@@ -4141,7 +4141,7 @@
       <c r="B3" t="s">
         <v>61</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="4">
         <f>VLOOKUP('Sales Region Lookup'!A3, 'By Search Term'!B:C, 2, FALSE)</f>
         <v>0.68</v>
       </c>
@@ -4157,7 +4157,7 @@
       <c r="B4" t="s">
         <v>61</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="4">
         <f>VLOOKUP('Sales Region Lookup'!A4, 'By Search Term'!B:C, 2, FALSE)</f>
         <v>0.67</v>
       </c>
@@ -4173,7 +4173,7 @@
       <c r="B5" t="s">
         <v>61</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="4">
         <f>VLOOKUP('Sales Region Lookup'!A5, 'By Search Term'!B:C, 2, FALSE)</f>
         <v>0.73</v>
       </c>
@@ -4189,7 +4189,7 @@
       <c r="B6" t="s">
         <v>62</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="4">
         <f>VLOOKUP('Sales Region Lookup'!A6, 'By Search Term'!B:C, 2, FALSE)</f>
         <v>0.7</v>
       </c>
@@ -4205,7 +4205,7 @@
       <c r="B7" t="s">
         <v>62</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="4">
         <f>VLOOKUP('Sales Region Lookup'!A7, 'By Search Term'!B:C, 2, FALSE)</f>
         <v>0.76</v>
       </c>
@@ -4221,7 +4221,7 @@
       <c r="B8" t="s">
         <v>62</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="4">
         <f>VLOOKUP('Sales Region Lookup'!A8, 'By Search Term'!B:C, 2, FALSE)</f>
         <v>0.7</v>
       </c>
@@ -4237,7 +4237,7 @@
       <c r="B9" t="s">
         <v>62</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="4">
         <f>VLOOKUP('Sales Region Lookup'!A9, 'By Search Term'!B:C, 2, FALSE)</f>
         <v>0.68</v>
       </c>
@@ -4253,7 +4253,7 @@
       <c r="B10" t="s">
         <v>62</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="4">
         <f>VLOOKUP('Sales Region Lookup'!A10, 'By Search Term'!B:C, 2, FALSE)</f>
         <v>0.66</v>
       </c>
@@ -4269,7 +4269,7 @@
       <c r="B11" t="s">
         <v>62</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="4">
         <f>VLOOKUP('Sales Region Lookup'!A11, 'By Search Term'!B:C, 2, FALSE)</f>
         <v>0.66</v>
       </c>
@@ -4298,10 +4298,10 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="7">
         <v>0.67</v>
       </c>
       <c r="C16" s="1">
@@ -4309,10 +4309,10 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="7">
         <v>0.66</v>
       </c>
       <c r="C17" s="1">
@@ -4320,10 +4320,10 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="7">
         <v>0.68</v>
       </c>
       <c r="C18" s="1">
@@ -4331,10 +4331,10 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="7">
         <v>0.73</v>
       </c>
       <c r="C19" s="1">
@@ -4342,10 +4342,10 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="7">
         <v>0.7</v>
       </c>
       <c r="C20" s="1">
@@ -4353,10 +4353,10 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="7">
         <v>0.7</v>
       </c>
       <c r="C21" s="1">
@@ -4364,10 +4364,10 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="7">
         <v>0.68</v>
       </c>
       <c r="C22" s="1">
@@ -4375,10 +4375,10 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="7">
         <v>0.76</v>
       </c>
       <c r="C23" s="1">
@@ -4386,10 +4386,10 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B24" s="7">
         <v>0.67</v>
       </c>
       <c r="C24" s="1">
@@ -4397,10 +4397,10 @@
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="7">
         <v>0.66</v>
       </c>
       <c r="C25" s="1">
@@ -4408,10 +4408,10 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B26" s="7">
         <v>6.91</v>
       </c>
       <c r="C26" s="1">
